--- a/Employee_Reports_wi52/Sivagaran Ramanathan Q0128.xlsx
+++ b/Employee_Reports_wi52/Sivagaran Ramanathan Q0128.xlsx
@@ -52,14 +52,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
-        <bgColor rgb="00FFFACD"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFFACD"/>
+        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,117 +1068,117 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>EXPIRING SOON</t>
+          <t>EXPIRED</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Softwares &amp; Param. (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-018</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>18-Aug-2024</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>18-Aug-2026</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Control circuits (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-019</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>18-Aug-2024</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>18-Aug-2026</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="H15" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1230,53 +1230,53 @@
       <c r="K16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>LSME-CRG-M-014</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>12-Sep-2024</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>12-Sep-2026</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1427,90 +1427,90 @@
       <c r="K20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>STACKER CRANE AISLE MONTHLY PREVENTIVE MAINTENANCE (SOPs)</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-035</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2024</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2025</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
-        <v>-385</v>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="n">
+        <v>-393</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Endangered by Electricity A safety Training (SOPs)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2024</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>31-Jul-2025</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
-        <v>-385</v>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="H22" s="4" t="n">
+        <v>-393</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1611,213 +1611,213 @@
       <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Driven Wheel (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-009</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2025</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2026</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="H25" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Fork Flyer Chain (SOPs)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-010</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2025</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2026</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="H26" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Replacement of Stacker Crane Wire Rope (SOPs)</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr"/>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr"/>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2025</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>27-Jul-2026</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="H27" s="4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
+      <c r="H28" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="H29" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1854,11 +1854,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1882,20 +1882,20 @@
       <c r="E31" s="3" t="inlineStr"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2025</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2027</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>320</v>
+        <v>728</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1972,213 +1972,213 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Stacker Crane</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>29-Jun-2024</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>44.34%</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G3" s="5" t="n"/>
+      <c r="G3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ews Eq </t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>01-Nov-2023</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>38.00%</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Consignment Shuttle Tv</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>28-Jun-2025</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>46.90%</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n"/>
+      <c r="G5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Uld&amp;Bb-Tv</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>06-Oct-2024</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>48.11%</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n"/>
+      <c r="G6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Fmc Deck</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>65.00%</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. Kindly redo your exam the exam is not recorded properly</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n"/>
+      <c r="G7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Cs Hoist</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>65.43%</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. Kindly redo your exam the exam is not recorded properly</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
+      <c r="G8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Truck Dock</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>07-May-2024</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>69.38%</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>low percentage</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>This is a low mark, please retake the exam and improve your score. date is valid</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n"/>
+      <c r="G9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr"/>
